--- a/data/trans_orig/P6906-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6906-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33690</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>44405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14005</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50554</t>
+          <t>50710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62678</t>
+          <t>62529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>27787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51545</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>44945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73695</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90746</t>
+          <t>91548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>114504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>52487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66931</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147871</t>
+          <t>147909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176851</t>
+          <t>176621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38564</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87464</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107013</t>
+          <t>107321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61378</t>
+          <t>60927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140142</t>
+          <t>141117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164426</t>
+          <t>163712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37013</t>
+          <t>37010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>48207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>74100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93438</t>
+          <t>93435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122773</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42162</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>43056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54886</t>
+          <t>54748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88075</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133854</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177728</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345380</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384230</t>
+          <t>382619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159608</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183422</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>514699</t>
+          <t>514362</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>558573</t>
+          <t>560019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57229</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73645</t>
+          <t>73705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101243</t>
+          <t>101696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59747</t>
+          <t>59524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>67534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84532</t>
+          <t>83932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37907</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>54365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111639</t>
+          <t>111862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134994</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53907</t>
+          <t>49750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>70341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38140</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83770</t>
+          <t>83542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105142</t>
+          <t>105877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24611</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>35749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68102</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169978</t>
+          <t>172629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>225226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>257043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163951</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371082</t>
+          <t>368431</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>413094</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57494</t>
+          <t>55958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25262</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37386</t>
+          <t>37428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87448</t>
+          <t>87619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106286</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37006</t>
+          <t>37479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58605</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76117</t>
+          <t>75644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>94865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42812</t>
+          <t>43146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57929</t>
+          <t>57569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125976</t>
+          <t>124315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148050</t>
+          <t>148581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32441</t>
+          <t>33062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58987</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>75992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115811</t>
+          <t>116698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67365</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134773</t>
+          <t>132743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177346</t>
+          <t>177122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>248080</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>282636</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130601</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>388953</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>431526</t>
+          <t>433556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8059</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>52,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2690</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>51,31%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9814</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42015</t>
+          <t>42180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67984</t>
+          <t>69890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91719</t>
+          <t>92873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28754</t>
+          <t>29132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>66399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83526</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48680</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>61249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120117</t>
+          <t>118696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140702</t>
+          <t>140263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44673</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68658</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>96088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110276</t>
+          <t>110697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140354</t>
+          <t>139518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194844</t>
+          <t>197520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228279</t>
+          <t>229569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39794</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>61570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40944</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83149</t>
+          <t>83243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98974</t>
+          <t>99605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -11385,97 +11385,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>74,74%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>566</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>71,02%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106237</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127376</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181106</t>
+          <t>177729</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>256590</t>
+          <t>257066</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>289380</t>
+          <t>290226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247978</t>
+          <t>248087</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>289821</t>
+          <t>290422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>512614</t>
+          <t>515991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>566344</t>
+          <t>565481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
